--- a/data/review-sheet.xlsx
+++ b/data/review-sheet.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>être (forme partagée), est (forme partagée), était, sont, es, été (forme partagée), suis (forme partagée), êtes (+33 more in data/pilot-300.json)</t>
+          <t>être (forme partagée), est (forme partagée), était, sont, es, été (forme partagée), suis (forme partagée), êtes (+33 autres formes)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>avoir (forme partagée), a (forme partagée), ai, avait, as (forme partagée), ont, avez, eu (+38 more in data/pilot-300.json)</t>
+          <t>avoir (forme partagée), a (forme partagée), ai, avait, as (forme partagée), ont, avez, eu (+38 autres formes)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>faire, fait (forme partagée), fais, faisait, faites (forme partagée), fit, font, fera (+32 more in data/pilot-300.json)</t>
+          <t>faire, fait (forme partagée), fais, faisait, faites (forme partagée), fit, font, fera (+32 autres formes)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>aller (forme partagée), va (forme partagée), vais, allez (forme partagée), vas, allons, allait, vont (+31 more in data/pilot-300.json)</t>
+          <t>aller (forme partagée), va (forme partagée), vais, allez (forme partagée), vas, allons, allait, vont (+31 autres formes)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>dire (forme partagée), dit (forme partagée), dis, disait, dites (forme partagée), dirait, disais, disent (+24 more in data/pilot-300.json)</t>
+          <t>dire (forme partagée), dit (forme partagée), dis, disait, dites (forme partagée), dirait, disais, disent (+24 autres formes)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>pouvoir (forme partagée), peux, peut, pu, pouvait, pourrait, pouvez, pourrais (+33 more in data/pilot-300.json)</t>
+          <t>pouvoir (forme partagée), peux, peut, pu, pouvait, pourrait, pouvez, pourrais (+33 autres formes)</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>vouloir (forme partagée), veux, veut, voulez (forme partagée), voulais, voulait, voulu (forme partagée), voudrais (+29 more in data/pilot-300.json)</t>
+          <t>vouloir (forme partagée), veux, veut, voulez (forme partagée), voulais, voulait, voulu (forme partagée), voudrais (+29 autres formes)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>voir, vu (forme partagée), vois, voit, voyez, voyait, voyons, vue (forme partagée) (+26 more in data/pilot-300.json)</t>
+          <t>voir, vu (forme partagée), vois, voit, voyez, voyait, voyons, vue (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>savoir (forme partagée), sais (forme partagée), sait, savez, savais, savait, su (forme partagée), savent (+32 more in data/pilot-300.json)</t>
+          <t>savoir (forme partagée), sais (forme partagée), sait, savez, savais, savait, su (forme partagée), savent (+32 autres formes)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>devoir (forme partagée), dois, doit (forme partagée), dû (forme partagée), devait, devrais, devrait, devez (+30 more in data/pilot-300.json)</t>
+          <t>devoir (forme partagée), dois, doit (forme partagée), dû (forme partagée), devait, devrais, devrait, devez (+30 autres formes)</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>venir, viens, vient, venu (forme partagée), venez, venait, venue (forme partagée), viennent (+27 more in data/pilot-300.json)</t>
+          <t>venir, viens, vient, venu (forme partagée), venez, venait, venue (forme partagée), viennent (+27 autres formes)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>prendre, pris (forme partagée), prends, prend, prenez, prit, prenait, prise (forme partagée) (+28 more in data/pilot-300.json)</t>
+          <t>prendre, pris (forme partagée), prends, prend, prenez, prit, prenait, prise (forme partagée) (+28 autres formes)</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>parler (forme partagée), parle, parlé (forme partagée), parlait, parles, parlez, parlons, parlent (+27 more in data/pilot-300.json)</t>
+          <t>parler (forme partagée), parle, parlé (forme partagée), parlait, parles, parlez, parlons, parlent (+27 autres formes)</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>suivre, suis (forme partagée), suivi (forme partagée), suivez, suit, suivait, suivit, suivant (forme partagée) (+26 more in data/pilot-300.json)</t>
+          <t>suivre, suis (forme partagée), suivi (forme partagée), suivez, suit, suivait, suivit, suivant (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>passer (forme partagée), passe (forme partagée), passé (forme partagée), passait, passa, passant (forme partagée), passent, passez (+26 more in data/pilot-300.json)</t>
+          <t>passer (forme partagée), passe (forme partagée), passé (forme partagée), passait, passa, passant (forme partagée), passent, passez (+26 autres formes)</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>croire, crois, croyais, croyez, cru (forme partagée), croit, croyait, croient (+28 more in data/pilot-300.json)</t>
+          <t>croire, crois, croyais, croyez, cru (forme partagée), croit, croyait, croient (+28 autres formes)</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>aimer, aime, aimerais, aimes, aimait, aimé (forme partagée), aimais, aimez (+28 more in data/pilot-300.json)</t>
+          <t>aimer, aime, aimerais, aimes, aimait, aimé (forme partagée), aimais, aimez (+28 autres formes)</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>penser, pense, pensais, pensé, penses, pensez, pensait, pensa (+24 more in data/pilot-300.json)</t>
+          <t>penser, pense, pensais, pensé, penses, pensez, pensait, pensa (+24 autres formes)</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>trouver, trouvé (forme partagée), trouve, trouvait, trouves, trouvez, trouva, trouvée (forme partagée) (+27 more in data/pilot-300.json)</t>
+          <t>trouver, trouvé (forme partagée), trouve, trouvait, trouves, trouvez, trouva, trouvée (forme partagée) (+27 autres formes)</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>regarder, regarde, regardez, regardait, regarda, regardé, regardant (forme partagée), regardais (+24 more in data/pilot-300.json)</t>
+          <t>regarder, regarde, regardez, regardait, regarda, regardé, regardant (forme partagée), regardais (+24 autres formes)</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>laisser, laisse (forme partagée), laissez, laissé (forme partagée), laissait, laissa, laissant, laisses (forme partagée) (+25 more in data/pilot-300.json)</t>
+          <t>laisser, laisse (forme partagée), laissez, laissé (forme partagée), laissait, laissa, laissant, laisses (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>donner (forme partagée), donne (forme partagée), donné (forme partagée), donnait, donnez, donna, donnent, donnes (forme partagée) (+26 more in data/pilot-300.json)</t>
+          <t>donner (forme partagée), donne (forme partagée), donné (forme partagée), donnait, donnez, donna, donnent, donnes (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>mettre, mis (forme partagée), mit, mets (forme partagée), met, mettez, mettait, mise (forme partagée) (+26 more in data/pilot-300.json)</t>
+          <t>mettre, mis (forme partagée), mit, mets (forme partagée), met, mettez, mettait, mise (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>attendre, attends, attendez, attend, attendait, attendant (forme partagée), attendais, attendu (forme partagée) (+28 more in data/pilot-300.json)</t>
+          <t>attendre, attends, attendez, attend, attendait, attendant (forme partagée), attendais, attendu (forme partagée) (+28 autres formes)</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>arriver, arrive, arrivé (forme partagée), arrivait, arrivent, arrivera, arrivée (forme partagée), arrivés (forme partagée) (+27 more in data/pilot-300.json)</t>
+          <t>arriver, arrive, arrivé (forme partagée), arrivait, arrivent, arrivera, arrivée (forme partagée), arrivés (forme partagée) (+27 autres formes)</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>demander, demande (forme partagée), demandé, demanda, demandait, demandais, demandez, demandes (forme partagée) (+23 more in data/pilot-300.json)</t>
+          <t>demander, demande (forme partagée), demandé, demanda, demandait, demandais, demandez, demandes (forme partagée) (+23 autres formes)</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>rester, reste (forme partagée), restait, restez, resté, resta, restes (forme partagée), restée (+26 more in data/pilot-300.json)</t>
+          <t>rester, reste (forme partagée), restait, restez, resté, resta, restes (forme partagée), restée (+26 autres formes)</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>appeler, appelle, appelé (forme partagée), appelait, appelez, appelles, appellent, appelée (+23 more in data/pilot-300.json)</t>
+          <t>appeler, appelle, appelé (forme partagée), appelait, appelez, appelles, appellent, appelée (+23 autres formes)</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>partir, parti (forme partagée), pars (forme partagée), partie (forme partagée), part (forme partagée), partez, partis (forme partagée), partons (+27 more in data/pilot-300.json)</t>
+          <t>partir, parti (forme partagée), pars (forme partagée), partie (forme partagée), part (forme partagée), partez, partis (forme partagée), partons (+27 autres formes)</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>connaître, connais (forme partagée), connaît, connu (forme partagée), connaissez, connaissait, connaissais, connaissent (+28 more in data/pilot-300.json)</t>
+          <t>connaître, connais (forme partagée), connaît, connu (forme partagée), connaissez, connaissait, connaissais, connaissent (+28 autres formes)</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>sortir (forme partagée), sors, sorti, sort (forme partagée), sortez, sortit, sortait, sortie (forme partagée) (+25 more in data/pilot-300.json)</t>
+          <t>sortir (forme partagée), sors, sorti, sort (forme partagée), sortez, sortit, sortait, sortie (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>comprendre, comprends, compris (forme partagée), comprenez, comprend, comprenait, comprit, comprenais (+25 more in data/pilot-300.json)</t>
+          <t>comprendre, comprends, compris (forme partagée), comprenez, comprend, comprenait, comprit, comprenais (+25 autres formes)</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>arrêter, arrête, arrêtez, arrêté (forme partagée), arrêta, arrêtait, arrêtée (forme partagée), arrêtes (+25 more in data/pilot-300.json)</t>
+          <t>arrêter, arrête, arrêtez, arrêté (forme partagée), arrêta, arrêtait, arrêtée (forme partagée), arrêtes (+25 autres formes)</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>entendre, entendu (forme partagée), entends, entend, entendait, entendit, entendez, entendais (+28 more in data/pilot-300.json)</t>
+          <t>entendre, entendu (forme partagée), entends, entend, entendait, entendit, entendez, entendais (+28 autres formes)</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>mourir, mort (forme partagée), morte (forme partagée), morts (forme partagée), meurt, meurs, meurent, meure (+27 more in data/pilot-300.json)</t>
+          <t>mourir, mort (forme partagée), morte (forme partagée), morts (forme partagée), meurt, meurs, meurent, meure (+27 autres formes)</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>sentir, sens (forme partagée), sentait, sent, sentais, senti (forme partagée), sentit, sentez (+26 more in data/pilot-300.json)</t>
+          <t>sentir, sens (forme partagée), sentait, sent, sentais, senti (forme partagée), sentit, sentez (+26 autres formes)</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>tenir, tenait, tient, tiens (forme partagée), tenez, tenu (forme partagée), tenant (forme partagée), tenaient (+26 more in data/pilot-300.json)</t>
+          <t>tenir, tenait, tient, tiens (forme partagée), tenez, tenu (forme partagée), tenant (forme partagée), tenaient (+26 autres formes)</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>chercher, cherche, cherchait, cherché, cherchez, cherches, cherchais, cherchant (+25 more in data/pilot-300.json)</t>
+          <t>chercher, cherche, cherchait, cherché, cherchez, cherches, cherchais, cherchant (+25 autres formes)</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>revenir, reviens, revient (forme partagée), revenu (forme partagée), revint, revenait, reviendra, revenue (forme partagée) (+26 more in data/pilot-300.json)</t>
+          <t>revenir, reviens, revient (forme partagée), revenu (forme partagée), revint, revenait, reviendra, revenue (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>tuer, tué (forme partagée), tue (forme partagée), tuée (forme partagée), tuez, tués (forme partagée), tuerai, tuera (+23 more in data/pilot-300.json)</t>
+          <t>tuer, tué (forme partagée), tue (forme partagée), tuée (forme partagée), tuez, tués (forme partagée), tuerai, tuera (+23 autres formes)</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>rendre, rend, rends, rendu (forme partagée), rendait, rendez, rendit, rendent (+27 more in data/pilot-300.json)</t>
+          <t>rendre, rend, rends, rendu (forme partagée), rendait, rendez, rendit, rendent (+27 autres formes)</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>finir, fini (forme partagée), finit, finie (forme partagée), finis (forme partagée), finissait, finira, finissent (+23 more in data/pilot-300.json)</t>
+          <t>finir, fini (forme partagée), finit, finie (forme partagée), finis (forme partagée), finissait, finira, finissent (+23 autres formes)</t>
         </is>
       </c>
       <c r="F207" s="6" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>devenir (forme partagée), devenu, devient, devenue, devenait, deviens, devenus, devint (+29 more in data/pilot-300.json)</t>
+          <t>devenir (forme partagée), devenu, devient, devenue, devenait, deviens, devenus, devint (+29 autres formes)</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>vivre (forme partagée), vit (forme partagée), vécu (forme partagée), vivait, vivent, vis (forme partagée), vivaient, vivons (+26 more in data/pilot-300.json)</t>
+          <t>vivre (forme partagée), vit (forme partagée), vécu (forme partagée), vivait, vivent, vis (forme partagée), vivaient, vivons (+26 autres formes)</t>
         </is>
       </c>
       <c r="F209" s="6" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>essayer, essaie, essayé, essaye, essayez, essayait, essayais, essayant (+37 more in data/pilot-300.json)</t>
+          <t>essayer, essaie, essayé, essaye, essayez, essayait, essayais, essayant (+37 autres formes)</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>perdre, perdu (forme partagée), perd, perds, perdue (forme partagée), perdait, perdus (forme partagée), perdez (+27 more in data/pilot-300.json)</t>
+          <t>perdre, perdu (forme partagée), perd, perds, perdue (forme partagée), perdait, perdus (forme partagée), perdez (+27 autres formes)</t>
         </is>
       </c>
       <c r="F215" s="6" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>jouer, joue (forme partagée), joué (forme partagée), jouait, joues (forme partagée), jouent, jouez, jouant (+24 more in data/pilot-300.json)</t>
+          <t>jouer, joue (forme partagée), joué (forme partagée), jouait, joues (forme partagée), jouent, jouez, jouant (+24 autres formes)</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>ouvrir, ouvre, ouvert (forme partagée), ouvrit, ouvrez, ouverte (forme partagée), ouvrait, ouvrant (forme partagée) (+25 more in data/pilot-300.json)</t>
+          <t>ouvrir, ouvre, ouvert (forme partagée), ouvrit, ouvrez, ouverte (forme partagée), ouvrait, ouvrant (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>commencer, commence, commencé, commençait, commença, commencent, commençaient, commençais (+25 more in data/pilot-300.json)</t>
+          <t>commencer, commence, commencé, commençait, commença, commencent, commençaient, commençais (+25 autres formes)</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>tomber, tombe (forme partagée), tombé (forme partagée), tombée (forme partagée), tombait, tomba, tombent, tombés (forme partagée) (+24 more in data/pilot-300.json)</t>
+          <t>tomber, tombe (forme partagée), tombé (forme partagée), tombée (forme partagée), tombait, tomba, tombent, tombés (forme partagée) (+24 autres formes)</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>entrer, entre (forme partagée), entrez, entré, entra, entrait, entrée (forme partagée), entrés (+25 more in data/pilot-300.json)</t>
+          <t>entrer, entre (forme partagée), entrez, entré, entra, entrait, entrée (forme partagée), entrés (+25 autres formes)</t>
         </is>
       </c>
       <c r="F233" s="6" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>aider, aide (forme partagée), aidez, aidé, aidera, aides (forme partagée), aidée, aidait (+24 more in data/pilot-300.json)</t>
+          <t>aider, aide (forme partagée), aidez, aidé, aidera, aides (forme partagée), aidée, aidait (+24 autres formes)</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>rentrer, rentre, rentré (forme partagée), rentrée (forme partagée), rentrez, rentrant (forme partagée), rentres, rentrons (+24 more in data/pilot-300.json)</t>
+          <t>rentrer, rentre, rentré (forme partagée), rentrée (forme partagée), rentrez, rentrant (forme partagée), rentres, rentrons (+24 autres formes)</t>
         </is>
       </c>
       <c r="F243" s="6" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>sembler, semblait, semble, semblaient, semblent, sembla, semblé, semblant (forme partagée) (+12 more in data/pilot-300.json)</t>
+          <t>sembler, semblait, semble, semblaient, semblent, sembla, semblé, semblant (forme partagée) (+12 autres formes)</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>tirer, tire (forme partagée), tiré (forme partagée), tirez, tira, tirait, tirant (forme partagée), tirent (+25 more in data/pilot-300.json)</t>
+          <t>tirer, tire (forme partagée), tiré (forme partagée), tirez, tira, tirait, tirant (forme partagée), tirent (+25 autres formes)</t>
         </is>
       </c>
       <c r="F249" s="6" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>porter (forme partagée), porte (forme partagée), portait, porté, portant (forme partagée), portaient, portent, portes (forme partagée) (+24 more in data/pilot-300.json)</t>
+          <t>porter (forme partagée), porte (forme partagée), portait, porté, portant (forme partagée), portaient, portent, portes (forme partagée) (+24 autres formes)</t>
         </is>
       </c>
       <c r="F251" s="6" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>écouter, écoute (forme partagée), écoutez, écoutait, écouté, écoutes (forme partagée), écoutant (forme partagée), écoutais (+23 more in data/pilot-300.json)</t>
+          <t>écouter, écoute (forme partagée), écoutez, écoutait, écouté, écoutes (forme partagée), écoutant (forme partagée), écoutais (+23 autres formes)</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>oublier, oublié (forme partagée), oublie (forme partagée), oubliez, oublierai, oublies (forme partagée), oubliais, oubliée (forme partagée) (+25 more in data/pilot-300.json)</t>
+          <t>oublier, oublié (forme partagée), oublie (forme partagée), oubliez, oublierai, oublies (forme partagée), oubliais, oubliée (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>manger (forme partagée), mange, mangé, mangeait, manges, mangent, mangez, mangeant (+26 more in data/pilot-300.json)</t>
+          <t>manger (forme partagée), mange, mangé, mangeait, manges, mangent, mangez, mangeant (+26 autres formes)</t>
         </is>
       </c>
       <c r="F261" s="6" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>plaire, plaît, plaisait, plais, plairait, plaira, plaisent, plaise (+20 more in data/pilot-300.json)</t>
+          <t>plaire, plaît, plaisait, plais, plairait, plaira, plaisent, plaise (+20 autres formes)</t>
         </is>
       </c>
       <c r="F263" s="6" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>répondre, répondit, répondu, réponds, répond, répondait, répondez, répondis (+23 more in data/pilot-300.json)</t>
+          <t>répondre, répondit, répondu, réponds, répond, répondait, répondez, répondis (+23 autres formes)</t>
         </is>
       </c>
       <c r="F271" s="6" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>asseoir, assis (forme partagée), assieds, asseyez, assise (forme partagée), assit, assied, asseyait (+35 more in data/pilot-300.json)</t>
+          <t>asseoir, assis (forme partagée), assieds, asseyez, assise (forme partagée), assit, assied, asseyait (+35 autres formes)</t>
         </is>
       </c>
       <c r="F273" s="6" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>retrouver, retrouve, retrouvé, retrouvait, retrouva, retrouvée, retrouvés, retrouvera (+25 more in data/pilot-300.json)</t>
+          <t>retrouver, retrouve, retrouvé, retrouvait, retrouva, retrouvée, retrouvés, retrouvera (+25 autres formes)</t>
         </is>
       </c>
       <c r="F275" s="6" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>marcher, marche (forme partagée), marché (forme partagée), marchait, marchant (forme partagée), marchent, marcha, marchera (+23 more in data/pilot-300.json)</t>
+          <t>marcher, marche (forme partagée), marché (forme partagée), marchait, marchant (forme partagée), marchent, marcha, marchera (+23 autres formes)</t>
         </is>
       </c>
       <c r="F287" s="6" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>travailler, travaille, travaillé (forme partagée), travaillait, travaillent, travaillez, travailles, travaillais (+25 more in data/pilot-300.json)</t>
+          <t>travailler, travaille, travaillé (forme partagée), travaillait, travaillent, travaillez, travailles, travaillais (+25 autres formes)</t>
         </is>
       </c>
       <c r="F289" s="6" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>monter, monte, montait, monté (forme partagée), monta, montaient, montée (forme partagée), montent (+23 more in data/pilot-300.json)</t>
+          <t>monter, monte, montait, monté (forme partagée), monta, montaient, montée (forme partagée), montent (+23 autres formes)</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>changer, changé (forme partagée), change (forme partagée), changera, changeait, changent, changea, changez (+24 more in data/pilot-300.json)</t>
+          <t>changer, changé (forme partagée), change (forme partagée), changera, changeait, changent, changea, changez (+24 autres formes)</t>
         </is>
       </c>
       <c r="F295" s="6" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="E297" s="6" t="inlineStr">
         <is>
-          <t>dormir, dort, dors, dormi, dormait, dormais, dorment, dormez (+23 more in data/pilot-300.json)</t>
+          <t>dormir, dort, dors, dormi, dormait, dormais, dorment, dormez (+23 autres formes)</t>
         </is>
       </c>
       <c r="F297" s="6" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="E299" s="6" t="inlineStr">
         <is>
-          <t>écrire, écrit (forme partagée), écris, écrivait, écrivais, écrivez, écrite (forme partagée), écrivit (+25 more in data/pilot-300.json)</t>
+          <t>écrire, écrit (forme partagée), écris, écrivait, écrivais, écrivez, écrite (forme partagée), écrivit (+25 autres formes)</t>
         </is>
       </c>
       <c r="F299" s="6" t="inlineStr">

--- a/data/review-sheet.xlsx
+++ b/data/review-sheet.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Mots" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Changes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mots'!$A$1:$H$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Changes'!$A$1:$E$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -101,6 +103,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -690,7 +695,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>je (forme partagée)</t>
+          <t>je (forme partagée), j'</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -718,7 +723,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>ne, n', n (forme partagée)</t>
+          <t>ne, n'</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1474,7 +1479,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>me (forme partagée)</t>
+          <t>me (forme partagée), m'</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1614,7 +1619,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>ce (forme partagée)</t>
+          <t>ce (forme partagée), c'</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1726,7 +1731,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>que (forme partagée)</t>
+          <t>que (forme partagée), qu'</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -1754,7 +1759,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>que (forme partagée)</t>
+          <t>que (forme partagée), qu'</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -1970,19 +1975,15 @@
           <t>tout</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C51" s="6" t="inlineStr"/>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>adjectif indéfini</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>tous (forme partagée), tout (forme partagée), toute (forme partagée), toutes (forme partagée)</t>
+          <t>tout (forme partagée), tous, toute, toutes</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -1999,18 +2000,18 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>tout</t>
+          <t>en</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>adjectif indéfini</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>tout (forme partagée)</t>
+          <t>en (forme partagée)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -2027,7 +2028,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ils</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr"/>
@@ -2038,7 +2039,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>en (forme partagée)</t>
+          <t>ils</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2055,18 +2056,18 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>ils</t>
+          <t>comme</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr"/>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>ils</t>
+          <t>comme (forme partagée)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -2083,18 +2084,18 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>comme</t>
+          <t>le</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr"/>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>comme (forme partagée)</t>
+          <t>le (forme partagée), l'</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -2111,7 +2112,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>moi</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr"/>
@@ -2122,7 +2123,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>le (forme partagée)</t>
+          <t>moi (forme partagée)</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -2139,18 +2140,18 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>moi</t>
+          <t>par</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr"/>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>moi (forme partagée)</t>
+          <t>par (forme partagée)</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -2167,18 +2168,18 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>par</t>
+          <t>non</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>par (forme partagée)</t>
+          <t>non (forme partagée)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -2195,18 +2196,18 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>ce</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr"/>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>adjectif démonstratif</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>non (forme partagée)</t>
+          <t>ce (forme partagée)</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2223,18 +2224,18 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ce</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>adjectif démonstratif</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>ce (forme partagée)</t>
+          <t>sa (forme partagée)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -2251,18 +2252,18 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>te</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr"/>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>sa (forme partagée)</t>
+          <t>t', te</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -2279,18 +2280,18 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>te</t>
+          <t>devoir</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr"/>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>t', te</t>
+          <t>devoir (forme partagée), dois, doit (forme partagée), dû (forme partagée), devait, devrais, devrait, devez (+30 autres formes)</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -2307,7 +2308,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>devoir</t>
+          <t>venir</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr"/>
@@ -2318,7 +2319,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>devoir (forme partagée), dois, doit (forme partagée), dû (forme partagée), devait, devrais, devrait, devez (+30 autres formes)</t>
+          <t>venir, viens, vient, venu (forme partagée), venez, venait, venue (forme partagée), viennent (+27 autres formes)</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2335,18 +2336,18 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>venir</t>
+          <t>où</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>venir, viens, vient, venu (forme partagée), venez, venait, venue (forme partagée), viennent (+27 autres formes)</t>
+          <t>où (forme partagée)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -2369,7 +2370,7 @@
       <c r="C65" s="6" t="inlineStr"/>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>pronom interrogatif</t>
+          <t>pronom relatif</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2391,18 +2392,18 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>où</t>
+          <t>cette</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>pronom relatif</t>
+          <t>adjectif démonstratif</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>où (forme partagée)</t>
+          <t>cette</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -2419,18 +2420,18 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>cette</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr"/>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>adjectif démonstratif</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>cette</t>
+          <t>ma (forme partagée)</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -2447,18 +2448,18 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>ma (forme partagée)</t>
+          <t>ou (forme partagée)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -2475,18 +2476,18 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>rien</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr"/>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>pronom indéfini</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>ou (forme partagée)</t>
+          <t>rien (forme partagée)</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -2503,18 +2504,18 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>rien</t>
+          <t>ses</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>pronom indéfini</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>rien (forme partagée)</t>
+          <t>ses (forme partagée)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -2531,18 +2532,18 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>ses</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr"/>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>ses (forme partagée)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -2559,18 +2560,18 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>prendre</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>prendre, pris (forme partagée), prends, prend, prenez, prit, prenait, prise (forme partagée) (+28 autres formes)</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -2587,18 +2588,18 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>prendre</t>
+          <t>quand</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr"/>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>prendre, pris (forme partagée), prends, prend, prenez, prit, prenait, prise (forme partagée) (+28 autres formes)</t>
+          <t>quand (forme partagée)</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -2615,18 +2616,18 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>quand</t>
+          <t>sans</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr"/>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>quand (forme partagée)</t>
+          <t>sans</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -2643,18 +2644,18 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>sans</t>
+          <t>là</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr"/>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>sans</t>
+          <t>là (forme partagée)</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -2671,18 +2672,18 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>là</t>
+          <t>parler</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr"/>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>là (forme partagée)</t>
+          <t>parler (forme partagée), parle, parlé (forme partagée), parlait, parles, parlez, parlons, parlent (+27 autres formes)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -2699,7 +2700,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>parler</t>
+          <t>suivre</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr"/>
@@ -2710,7 +2711,7 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>parler (forme partagée), parle, parlé (forme partagée), parlait, parles, parlez, parlons, parlent (+27 autres formes)</t>
+          <t>suivre, suis (forme partagée), suivi (forme partagée), suivez, suit, suivait, suivit, suivant (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -2727,18 +2728,18 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>suivre</t>
+          <t>si</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr"/>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>suivre, suis (forme partagée), suivi (forme partagée), suivez, suit, suivait, suivit, suivant (forme partagée) (+26 autres formes)</t>
+          <t>si (forme partagée)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -2755,18 +2756,18 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>toi</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr"/>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>si (forme partagée)</t>
+          <t>toi</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -2783,18 +2784,18 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>toi</t>
+          <t>falloir</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr"/>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>toi</t>
+          <t>falloir, faut, fallait, faudrait, faudra, fallu, fallut, faille</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -2811,18 +2812,18 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>falloir</t>
+          <t>ici</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr"/>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>falloir, faut, fallait, faudrait, faudra, fallu, fallut, fallût</t>
+          <t>ici (forme partagée)</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -2839,18 +2840,22 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>ici</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr"/>
+          <t>la chose</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>ici (forme partagée)</t>
+          <t>chose, choses (forme partagée)</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -2867,22 +2872,18 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>la chose</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>alors</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr"/>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>chose, choses (forme partagée)</t>
+          <t>alors</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -2899,18 +2900,18 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>alors</t>
+          <t>ces</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr"/>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>adjectif démonstratif</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>alors</t>
+          <t>ces</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -2927,18 +2928,18 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>ces</t>
+          <t>aussi</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr"/>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>adjectif démonstratif</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>ces</t>
+          <t>aussi</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -2955,7 +2956,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>aussi</t>
+          <t>encore</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr"/>
@@ -2966,7 +2967,7 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>aussi</t>
+          <t>encore</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -2983,18 +2984,18 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>encore</t>
+          <t>aux</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr"/>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>article défini</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>encore</t>
+          <t>aux</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -3011,18 +3012,18 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>aux</t>
+          <t>très</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>article défini</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>aux</t>
+          <t>très</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -3039,7 +3040,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>très</t>
+          <t>tout</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr"/>
@@ -3050,7 +3051,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>très</t>
+          <t>tout (forme partagée)</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -3067,18 +3068,18 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>tout</t>
+          <t>passer</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>tout (forme partagée)</t>
+          <t>passer (forme partagée), passe (forme partagée), passé (forme partagée), passait, passa, passant (forme partagée), passent, passez (+26 autres formes)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -3095,7 +3096,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>passer</t>
+          <t>croire</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr"/>
@@ -3106,7 +3107,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>passer (forme partagée), passe (forme partagée), passé (forme partagée), passait, passa, passant (forme partagée), passent, passez (+26 autres formes)</t>
+          <t>croire, crois, croyais, croyez, cru (forme partagée), croit, croyait, croient (+28 autres formes)</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -3123,18 +3124,18 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>croire</t>
+          <t>les</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr"/>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>croire, crois, croyais, croyez, cru (forme partagée), croit, croyait, croient (+28 autres formes)</t>
+          <t>les (forme partagée)</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -3151,18 +3152,22 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>les</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr"/>
+          <t>petit</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>les (forme partagée)</t>
+          <t>petit (forme partagée), petite (forme partagée), petits (forme partagée), petites (forme partagée)</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -3179,22 +3184,18 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>petit</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>deux</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr"/>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>adjectif numéral</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>petit (forme partagée), petite (forme partagée), petits (forme partagée), petites (forme partagée)</t>
+          <t>deux</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -3211,18 +3212,22 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>deux</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr"/>
+          <t>l'homme</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>adjectif numéral</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>deux</t>
+          <t>homme, hommes</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -3239,22 +3244,18 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>le homme</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>jamais</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr"/>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>homme, hommes</t>
+          <t>jamais</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -3271,18 +3272,18 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>jamais</t>
+          <t>aimer</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr"/>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>jamais</t>
+          <t>aimer, aime, aimerais, aimes, aimait, aimé (forme partagée), aimais, aimez (+28 autres formes)</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -3299,18 +3300,22 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>aimer</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr"/>
+          <t>le jour</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>aimer, aime, aimerais, aimes, aimait, aimé (forme partagée), aimais, aimez (+28 autres formes)</t>
+          <t>jour, jours</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -3327,22 +3332,18 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>le jour</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>penser</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr"/>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>jour, jours</t>
+          <t>penser, pense, pensais, pensé, penses, pensez, pensait, pensa (+24 autres formes)</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -3359,18 +3360,22 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>penser</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr"/>
+          <t>bon</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>penser, pense, pensais, pensé, penses, pensez, pensait, pensa (+24 autres formes)</t>
+          <t>bon (forme partagée), bonne (forme partagée), bonnes (forme partagée), bons (forme partagée)</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -3387,22 +3392,18 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>bon</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>votre</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr"/>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>bon (forme partagée), bonne (forme partagée), bonnes (forme partagée), bons (forme partagée)</t>
+          <t>votre (forme partagée)</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
@@ -3419,18 +3420,18 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>votre</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr"/>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>votre (forme partagée)</t>
+          <t>la (forme partagée), l'</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -3447,18 +3448,22 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>la</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr"/>
+          <t>le temps</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>la (forme partagée)</t>
+          <t>temps</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -3475,22 +3480,18 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>le temps</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr"/>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>temps</t>
+          <t>si (forme partagée), s'</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -3507,18 +3508,18 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>trouver</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr"/>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>si (forme partagée)</t>
+          <t>trouver, trouvé (forme partagée), trouve, trouvait, trouves, trouvez, trouva, trouvée (forme partagée) (+27 autres formes)</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -3535,18 +3536,18 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>trouver</t>
+          <t>même</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr"/>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>trouver, trouvé (forme partagée), trouve, trouvait, trouves, trouvez, trouva, trouvée (forme partagée) (+27 autres formes)</t>
+          <t>même (forme partagée)</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -3563,18 +3564,18 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>même</t>
+          <t>tout</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr"/>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>pronom indéfini</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>même (forme partagée)</t>
+          <t>tout (forme partagée), tous</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
@@ -3591,18 +3592,18 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>tout</t>
+          <t>regarder</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr"/>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>pronom indéfini</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>tout (forme partagée)</t>
+          <t>regarder, regarde, regardez, regardait, regarda, regardé, regardant (forme partagée), regardais (+24 autres formes)</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -3619,7 +3620,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>regarder</t>
+          <t>laisser</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr"/>
@@ -3630,7 +3631,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>regarder, regarde, regardez, regardait, regarda, regardé, regardant (forme partagée), regardais (+24 autres formes)</t>
+          <t>laisser, laisse (forme partagée), laissez, laissé (forme partagée), laissait, laissa, laissant, laisses (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
@@ -3647,18 +3648,18 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>laisser</t>
+          <t>toujours</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr"/>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>laisser, laisse (forme partagée), laissez, laissé (forme partagée), laissait, laissa, laissant, laisses (forme partagée) (+25 autres formes)</t>
+          <t>toujours</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -3675,18 +3676,18 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>toujours</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>toujours</t>
+          <t>mes (forme partagée)</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -3703,18 +3704,18 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>donner</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>mes (forme partagée)</t>
+          <t>donner (forme partagée), donne (forme partagée), donné (forme partagée), donnait, donnez, donna, donnent, donnes (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -3731,7 +3732,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>donner</t>
+          <t>mettre</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr"/>
@@ -3742,7 +3743,7 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>donner (forme partagée), donne (forme partagée), donné (forme partagée), donnait, donnez, donna, donnent, donnes (forme partagée) (+26 autres formes)</t>
+          <t>mettre, mis (forme partagée), mit, mets (forme partagée), met, mettez, mettait, mise (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -3759,7 +3760,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>mettre</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr"/>
@@ -3770,7 +3771,7 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>mettre, mis (forme partagée), mit, mets (forme partagée), met, mettez, mettait, mise (forme partagée) (+26 autres formes)</t>
+          <t>attendre, attends, attendez, attend, attendait, attendant (forme partagée), attendais, attendu (forme partagée) (+28 autres formes)</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -3787,18 +3788,22 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>attendre</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr"/>
+          <t>la femme</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>attendre, attends, attendez, attend, attendait, attendant (forme partagée), attendais, attendu (forme partagée) (+28 autres formes)</t>
+          <t>femme, femmes</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -3815,7 +3820,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>la femme</t>
+          <t>la fois</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -3830,7 +3835,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>femme, femmes</t>
+          <t>fois</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -3847,22 +3852,18 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>la fois</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr"/>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>fois</t>
+          <t>ton (forme partagée)</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -3879,18 +3880,18 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>arriver</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr"/>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>ton (forme partagée)</t>
+          <t>arriver, arrive, arrivé (forme partagée), arrivait, arrivent, arrivera, arrivée (forme partagée), arrivés (forme partagée) (+27 autres formes)</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -3907,18 +3908,22 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>arriver</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr"/>
+          <t>le peu</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>arriver, arrive, arrivé (forme partagée), arrivait, arrivent, arrivera, arrivée (forme partagée), arrivés (forme partagée) (+27 autres formes)</t>
+          <t>peu (forme partagée)</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -3935,22 +3940,18 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>le peu</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>demander</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr"/>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>peu (forme partagée)</t>
+          <t>demander, demande (forme partagée), demandé, demanda, demandait, demandais, demandez, demandes (forme partagée) (+23 autres formes)</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -3967,18 +3968,22 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>demander</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr"/>
+          <t>grand</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>demander, demande (forme partagée), demandé, demanda, demandait, demandais, demandez, demandes (forme partagée) (+23 autres formes)</t>
+          <t>grand (forme partagée), grande (forme partagée), grands (forme partagée), grandes (forme partagée)</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
@@ -3995,22 +4000,22 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>grand</t>
+          <t>la vie</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>grand (forme partagée), grande (forme partagée), grands (forme partagée), grandes (forme partagée)</t>
+          <t>vie, vies</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -4027,22 +4032,22 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>la vie</t>
+          <t>seul</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>vie, vies</t>
+          <t>seul (forme partagée), seule (forme partagée), seuls (forme partagée), seules (forme partagée)</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
@@ -4059,22 +4064,18 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>seul</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>rester</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>seul (forme partagée), seule (forme partagée), seuls (forme partagée), seules (forme partagée)</t>
+          <t>rester, reste (forme partagée), restait, restez, resté, resta, restes (forme partagée), restée (+26 autres formes)</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -4091,18 +4092,22 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>rester</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr"/>
+          <t>la main</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>rester, reste (forme partagée), restait, restez, resté, resta, restes (forme partagée), restée (+26 autres formes)</t>
+          <t>main, mains</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
@@ -4119,22 +4124,18 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>quoi</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>notre</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>quoi (forme partagée)</t>
+          <t>notre (forme partagée)</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -4151,22 +4152,18 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>la main</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr"/>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>main, mains</t>
+          <t>autre (forme partagée), autres (forme partagée)</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
@@ -4183,18 +4180,18 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>notre</t>
+          <t>trop</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr"/>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>notre (forme partagée)</t>
+          <t>trop</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -4211,18 +4208,22 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>autre</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr"/>
+          <t>l'œil</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>autre (forme partagée), autres (forme partagée)</t>
+          <t>yeux, œil</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
@@ -4239,18 +4240,22 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>trop</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr"/>
+          <t>l'heure</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>trop</t>
+          <t>heure, heures</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -4267,22 +4272,18 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>le œil</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>appeler</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr"/>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>yeux, œil, œils</t>
+          <t>appeler, appelle, appelé (forme partagée), appelait, appelez, appelles, appellent, appelée (+23 autres formes)</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -4299,12 +4300,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>la heure</t>
+          <t>le père</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -4314,7 +4315,7 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>heure, heures</t>
+          <t>père, pères</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -4331,18 +4332,18 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>appeler</t>
+          <t>peut-être</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr"/>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>appeler, appelle, appelé (forme partagée), appelait, appelez, appelles, appellent, appelée (+23 autres formes)</t>
+          <t>peut-être</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -4359,22 +4360,18 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>le père</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>partir</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr"/>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>père, pères</t>
+          <t>partir, parti (forme partagée), pars (forme partagée), partie (forme partagée), part (forme partagée), partez, partis (forme partagée), partons (+27 autres formes)</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -4391,18 +4388,18 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>peut-être</t>
+          <t>connaître</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr"/>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>peut-être</t>
+          <t>connaître, connais (forme partagée), connaît, connu (forme partagée), connaissez, connaissait, connaissais, connaissent (+28 autres formes)</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
@@ -4419,18 +4416,22 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>partir</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr"/>
+          <t>le monde</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>partir, parti (forme partagée), pars (forme partagée), partie (forme partagée), part (forme partagée), partez, partis (forme partagée), partons (+27 autres formes)</t>
+          <t>monde, mondes</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -4447,18 +4448,22 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>connaître</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr"/>
+          <t>l'an</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>connaître, connais (forme partagée), connaît, connu (forme partagée), connaissez, connaissait, connaissais, connaissent (+28 autres formes)</t>
+          <t>ans, an</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
@@ -4475,22 +4480,18 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>le monde</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>pourquoi</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>monde, mondes</t>
+          <t>pourquoi (forme partagée)</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -4507,22 +4508,18 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>le an</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>maintenant</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr"/>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>ans, an</t>
+          <t>maintenant (forme partagée)</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
@@ -4539,18 +4536,18 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>pourquoi</t>
+          <t>chez</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr"/>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>pourquoi (forme partagée)</t>
+          <t>chez</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -4567,18 +4564,18 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>maintenant</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr"/>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>maintenant (forme partagée)</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
@@ -4595,18 +4592,18 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>chez</t>
+          <t>sortir</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>chez</t>
+          <t>sortir (forme partagée), sors, sorti, sort (forme partagée), sortez, sortit, sortait, sortie (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -4623,18 +4620,18 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>comprendre</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr"/>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>comprendre, comprends, compris (forme partagée), comprenez, comprend, comprenait, comprit, comprenais (+25 autres formes)</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
@@ -4651,18 +4648,18 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>sortir</t>
+          <t>est-ce que</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr"/>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>locution interrogative</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>sortir (forme partagée), sors, sorti, sort (forme partagée), sortez, sortit, sortait, sortie (forme partagée) (+25 autres formes)</t>
+          <t>est-ce que, est-ce qu'</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -4679,18 +4676,22 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>comprendre</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr"/>
+          <t>l'enfant</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>m/f</t>
+        </is>
+      </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>comprendre, comprends, compris (forme partagée), comprenez, comprend, comprenait, comprit, comprenais (+25 autres formes)</t>
+          <t>enfants, enfant</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
@@ -4707,18 +4708,18 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>est-ce que</t>
+          <t>arrêter</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr"/>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>est-ce que</t>
+          <t>arrêter, arrête, arrêtez, arrêté (forme partagée), arrêta, arrêtait, arrêtée (forme partagée), arrêtes (+25 autres formes)</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -4735,12 +4736,12 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>le enfant</t>
+          <t>la mère</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -4750,7 +4751,7 @@
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>enfants, enfant</t>
+          <t>mère, mères</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
@@ -4767,7 +4768,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>arrêter</t>
+          <t>entendre</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr"/>
@@ -4778,7 +4779,7 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>arrêter, arrête, arrêtez, arrêté (forme partagée), arrêta, arrêtait, arrêtée (forme partagée), arrêtes (+25 autres formes)</t>
+          <t>entendre, entendu (forme partagée), entends, entend, entendait, entendit, entendez, entendais (+28 autres formes)</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -4795,22 +4796,18 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>la mère</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>quelque</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr"/>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif indéfini</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>mère, mères</t>
+          <t>quelque (forme partagée)</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
@@ -4827,18 +4824,22 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>entendre</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr"/>
+          <t>la fille</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>entendre, entendu (forme partagée), entends, entend, entendait, entendit, entendez, entendais (+28 autres formes)</t>
+          <t>fille, filles</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -4855,18 +4856,18 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>quelque</t>
+          <t>après</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr"/>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>adjectif indéfini</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>quelque (forme partagée)</t>
+          <t>après (forme partagée)</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
@@ -4883,7 +4884,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>la fille</t>
+          <t>la tête</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -4898,7 +4899,7 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>fille, filles</t>
+          <t>tête, têtes</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -4915,18 +4916,18 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>après</t>
+          <t>déjà</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr"/>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>après (forme partagée)</t>
+          <t>déjà (forme partagée)</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
@@ -4943,22 +4944,22 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>la tête</t>
+          <t>sûr</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>tête, têtes</t>
+          <t>sûr, sûre, sûrs, sûres</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -4975,18 +4976,18 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>déjà</t>
+          <t>sous</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr"/>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>déjà (forme partagée)</t>
+          <t>sous (forme partagée)</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
@@ -5003,22 +5004,22 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>sûr</t>
+          <t>la nuit</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>sûr, sûre, sûrs, sûres</t>
+          <t>nuit (forme partagée), nuits</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -5035,18 +5036,22 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>sous</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr"/>
+          <t>le coup</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>sous (forme partagée)</t>
+          <t>coup, coups</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
@@ -5063,22 +5068,18 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>la nuit</t>
-        </is>
-      </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>mourir</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr"/>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>nuit (forme partagée), nuits</t>
+          <t>mourir, mort (forme partagée), morte (forme partagée), morts (forme partagée), meurt, meurs, meurent, meure (+27 autres formes)</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -5095,22 +5096,18 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>le coup</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>quoi</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr"/>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>pronom interrogatif</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>coup, coups</t>
+          <t>quoi (forme partagée)</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
@@ -5127,18 +5124,18 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>mourir</t>
+          <t>quoi</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr"/>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>pronom relatif</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>mourir, mort (forme partagée), morte (forme partagée), morts (forme partagée), meurt, meurs, meurent, meure (+27 autres formes)</t>
+          <t>quoi (forme partagée)</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -5155,18 +5152,22 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>quoi</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr"/>
+          <t>le dieu</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>pronom interrogatif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>quoi (forme partagée)</t>
+          <t>dieu, dieux</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
@@ -5183,18 +5184,22 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>quoi</t>
-        </is>
-      </c>
-      <c r="C162" s="5" t="inlineStr"/>
+          <t>beau</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>pronom relatif</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>quoi (forme partagée)</t>
+          <t>beau (forme partagée), belle (forme partagée), beaux, belles (forme partagée), bel</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
@@ -5211,22 +5216,18 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>le dieu</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>sentir</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr"/>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>dieu, dieux</t>
+          <t>sentir, sens (forme partagée), sentait, sent, sentais, senti (forme partagée), sentit, sentez (+26 autres formes)</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
@@ -5243,22 +5244,18 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>beau</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>tenir</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr"/>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>beau (forme partagée), belle (forme partagée), beaux, belles (forme partagée)</t>
+          <t>tenir, tenait, tient, tiens (forme partagée), tenez, tenu (forme partagée), tenant (forme partagée), tenaient (+26 autres formes)</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -5275,18 +5272,18 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>sentir</t>
+          <t>vraiment</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr"/>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>sentir, sens (forme partagée), sentait, sent, sentais, senti (forme partagée), sentit, sentez (+26 autres formes)</t>
+          <t>vraiment</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
@@ -5303,18 +5300,22 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>tenir</t>
-        </is>
-      </c>
-      <c r="C166" s="5" t="inlineStr"/>
+          <t>vrai</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>tenir, tenait, tient, tiens (forme partagée), tenez, tenu (forme partagée), tenant (forme partagée), tenaient (+26 autres formes)</t>
+          <t>vrai (forme partagée), vraie, vrais (forme partagée), vraies</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -5331,18 +5332,18 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>vraiment</t>
+          <t>cela</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr"/>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>pronom démonstratif</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>vraiment</t>
+          <t>cela (forme partagée)</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
@@ -5359,14 +5360,10 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>vrai</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>même</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr"/>
       <c r="D168" s="5" t="inlineStr">
         <is>
           <t>adjectif</t>
@@ -5374,7 +5371,7 @@
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>vrai (forme partagée), vraie, vrais (forme partagée), vraies</t>
+          <t>même (forme partagée), mêmes (forme partagée)</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
@@ -5391,18 +5388,18 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>cela</t>
+          <t>entre</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr"/>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>pronom démonstratif</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>cela (forme partagée)</t>
+          <t>entre (forme partagée)</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
@@ -5419,18 +5416,18 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>même</t>
+          <t>moins</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr"/>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>même (forme partagée), mêmes (forme partagée)</t>
+          <t>moins (forme partagée)</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
@@ -5447,7 +5444,7 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>entre</t>
+          <t>vers</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr"/>
@@ -5458,7 +5455,7 @@
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>entre (forme partagée)</t>
+          <t>vers (forme partagée)</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
@@ -5475,18 +5472,18 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>moins</t>
+          <t>dont</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr"/>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>pronom relatif</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>moins (forme partagée)</t>
+          <t>dont (forme partagée)</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -5503,18 +5500,22 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>vers</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr"/>
+          <t>la maison</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>vers (forme partagée)</t>
+          <t>maison, maisons</t>
         </is>
       </c>
       <c r="F173" s="6" t="inlineStr">
@@ -5531,18 +5532,22 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>dont</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr"/>
+          <t>l'air</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>pronom interrogatif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>dont (forme partagée)</t>
+          <t>air, airs</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -5559,18 +5564,18 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>dont</t>
+          <t>chercher</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr"/>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>pronom relatif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>dont (forme partagée)</t>
+          <t>chercher, cherche, cherchait, cherché, cherchez, cherches, cherchais, cherchant (+25 autres formes)</t>
         </is>
       </c>
       <c r="F175" s="6" t="inlineStr">
@@ -5587,12 +5592,12 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>la maison</t>
+          <t>le soir</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
@@ -5602,7 +5607,7 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>maison, maisons</t>
+          <t>soir, soirs</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -5619,22 +5624,18 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>le air</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr"/>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>pronom indéfini</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>air, airs</t>
+          <t>autre (forme partagée), autres</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
@@ -5651,18 +5652,18 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>chercher</t>
+          <t>leur / leurs</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr"/>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>chercher, cherche, cherchait, cherché, cherchez, cherches, cherchais, cherchant (+25 autres formes)</t>
+          <t>leurs (forme partagée), leur</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -5679,7 +5680,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>le moment</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -5694,7 +5695,7 @@
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>soir, soirs</t>
+          <t>moment, moments</t>
         </is>
       </c>
       <c r="F179" s="6" t="inlineStr">
@@ -5711,18 +5712,18 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>revenir</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr"/>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>pronom indéfini</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>autre (forme partagée)</t>
+          <t>revenir, reviens, revient (forme partagée), revenu (forme partagée), revint, revenait, reviendra, revenue (forme partagée) (+26 autres formes)</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -5739,18 +5740,18 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>leurs</t>
+          <t>avant</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr"/>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>leurs (forme partagée)</t>
+          <t>avant (forme partagée)</t>
         </is>
       </c>
       <c r="F181" s="6" t="inlineStr">
@@ -5767,22 +5768,18 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>le moment</t>
-        </is>
-      </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>nos</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr"/>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>moment, moments</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
@@ -5799,18 +5796,22 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>revenir</t>
-        </is>
-      </c>
-      <c r="C183" s="6" t="inlineStr"/>
+          <t>l'ami(e)</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>m/f</t>
+        </is>
+      </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>revenir, reviens, revient (forme partagée), revenu (forme partagée), revint, revenait, reviendra, revenue (forme partagée) (+26 autres formes)</t>
+          <t>ami (forme partagée), amis (forme partagée), amie (forme partagée), amies (forme partagée)</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
@@ -5827,18 +5828,18 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>avant</t>
+          <t>tuer</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr"/>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>avant (forme partagée)</t>
+          <t>tuer, tué (forme partagée), tue (forme partagée), tuée (forme partagée), tuez, tués (forme partagée), tuerai, tuera (+23 autres formes)</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
@@ -5855,18 +5856,18 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr"/>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>onomatopée</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>oh (forme partagée)</t>
         </is>
       </c>
       <c r="F185" s="6" t="inlineStr">
@@ -5883,22 +5884,18 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>le ami</t>
-        </is>
-      </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>puis</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr"/>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>ami (forme partagée), amis (forme partagée), amie (forme partagée), amies (forme partagée)</t>
+          <t>puis (forme partagée)</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
@@ -5915,18 +5912,18 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>tuer</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr"/>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>tuer, tué (forme partagée), tue (forme partagée), tuée (forme partagée), tuez, tués (forme partagée), tuerai, tuera (+23 autres formes)</t>
+          <t>comment (forme partagée)</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
@@ -5943,18 +5940,18 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>beaucoup</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr"/>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>onomatopée</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>oh (forme partagée)</t>
+          <t>beaucoup</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -5971,18 +5968,18 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>puis</t>
+          <t>quelques</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr"/>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>adjectif indéfini</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>puis (forme partagée)</t>
+          <t>quelques</t>
         </is>
       </c>
       <c r="F189" s="6" t="inlineStr">
@@ -5999,18 +5996,22 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="C190" s="5" t="inlineStr"/>
+          <t>le monsieur</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>comment (forme partagée)</t>
+          <t>monsieur, messieurs</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -6027,18 +6028,18 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>beaucoup</t>
+          <t>donc</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr"/>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>beaucoup</t>
+          <t>donc</t>
         </is>
       </c>
       <c r="F191" s="6" t="inlineStr">
@@ -6055,18 +6056,18 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>quelques</t>
+          <t>voilà</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr"/>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>adjectif indéfini</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>quelques</t>
+          <t>voilà</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
@@ -6083,22 +6084,18 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>le monsieur</t>
-        </is>
-      </c>
-      <c r="C193" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>mieux</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr"/>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>monsieur, messieurs</t>
+          <t>mieux (forme partagée)</t>
         </is>
       </c>
       <c r="F193" s="6" t="inlineStr">
@@ -6115,18 +6112,22 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>donc</t>
-        </is>
-      </c>
-      <c r="C194" s="5" t="inlineStr"/>
+          <t>premier</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>donc</t>
+          <t>première (forme partagée), premier (forme partagée), premiers (forme partagée), premières (forme partagée)</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
@@ -6143,18 +6144,18 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>voilà</t>
+          <t>trois</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr"/>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>adjectif numéral</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>voilà</t>
+          <t>trois</t>
         </is>
       </c>
       <c r="F195" s="6" t="inlineStr">
@@ -6171,18 +6172,18 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>mieux</t>
+          <t>ni</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr"/>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>mieux (forme partagée)</t>
+          <t>ni</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
@@ -6199,7 +6200,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>premier</t>
+          <t>le besoin</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -6209,12 +6210,12 @@
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>première (forme partagée), premier (forme partagée), premiers (forme partagée), premières (forme partagée)</t>
+          <t>besoin, besoins</t>
         </is>
       </c>
       <c r="F197" s="6" t="inlineStr">
@@ -6231,18 +6232,18 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>trois</t>
+          <t>depuis</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr"/>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>adjectif numéral</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>trois</t>
+          <t>depuis (forme partagée)</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
@@ -6259,18 +6260,18 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>ni</t>
+          <t>elles</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr"/>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>ni</t>
+          <t>elles</t>
         </is>
       </c>
       <c r="F199" s="6" t="inlineStr">
@@ -6287,7 +6288,7 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>le besoin</t>
+          <t>le les gens</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
@@ -6302,7 +6303,7 @@
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>besoin, besoins</t>
+          <t>gens</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
@@ -6319,18 +6320,18 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>depuis</t>
+          <t>cet</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr"/>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>adjectif démonstratif</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>depuis (forme partagée)</t>
+          <t>cet</t>
         </is>
       </c>
       <c r="F201" s="6" t="inlineStr">
@@ -6347,18 +6348,18 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>elles</t>
+          <t>merci</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr"/>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>onomatopée</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>elles</t>
+          <t>merci (forme partagée)</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
@@ -6375,22 +6376,18 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>le gens</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>m/f</t>
-        </is>
-      </c>
+          <t>rendre</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr"/>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>gens</t>
+          <t>rendre, rend, rends, rendu (forme partagée), rendait, rendez, rendit, rendent (+27 autres formes)</t>
         </is>
       </c>
       <c r="F203" s="6" t="inlineStr">
@@ -6407,18 +6404,18 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>cet</t>
+          <t>finir</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr"/>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>adjectif démonstratif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>cet</t>
+          <t>finir, fini (forme partagée), finit, finie (forme partagée), finis (forme partagée), finissait, finira, finissent (+23 autres formes)</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
@@ -6435,18 +6432,18 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>merci</t>
+          <t>devenir</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr"/>
       <c r="D205" s="6" t="inlineStr">
         <is>
-          <t>onomatopée</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>merci (forme partagée)</t>
+          <t>devenir (forme partagée), devenu, devient, devenue, devenait, deviens, devenus, devint (+29 autres formes)</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
@@ -6463,7 +6460,7 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>rendre</t>
+          <t>vivre</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr"/>
@@ -6474,7 +6471,7 @@
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>rendre, rend, rends, rendu (forme partagée), rendait, rendez, rendit, rendent (+27 autres formes)</t>
+          <t>vivre (forme partagée), vit (forme partagée), vécu (forme partagée), vivait, vivent, vis (forme partagée), vivaient, vivons (+26 autres formes)</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
@@ -6491,7 +6488,7 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>finir</t>
+          <t>essayer</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr"/>
@@ -6502,7 +6499,7 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>finir, fini (forme partagée), finit, finie (forme partagée), finis (forme partagée), finissait, finira, finissent (+23 autres formes)</t>
+          <t>essayer, essaie, essayé, essaye, essayez, essayait, essayais, essayant (+37 autres formes)</t>
         </is>
       </c>
       <c r="F207" s="6" t="inlineStr">
@@ -6519,18 +6516,22 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>devenir</t>
-        </is>
-      </c>
-      <c r="C208" s="5" t="inlineStr"/>
+          <t>le nom</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>devenir (forme partagée), devenu, devient, devenue, devenait, deviens, devenus, devint (+29 autres formes)</t>
+          <t>nom, noms</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
@@ -6547,18 +6548,18 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>vivre</t>
+          <t>pourquoi</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr"/>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>vivre (forme partagée), vit (forme partagée), vécu (forme partagée), vivait, vivent, vis (forme partagée), vivaient, vivons (+26 autres formes)</t>
+          <t>pourquoi (forme partagée)</t>
         </is>
       </c>
       <c r="F209" s="6" t="inlineStr">
@@ -6575,18 +6576,22 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>essayer</t>
-        </is>
-      </c>
-      <c r="C210" s="5" t="inlineStr"/>
+          <t>la porte</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>essayer, essaie, essayé, essaye, essayez, essayait, essayais, essayant (+37 autres formes)</t>
+          <t>porte (forme partagée), portes (forme partagée)</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
@@ -6603,22 +6608,18 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>le nom</t>
-        </is>
-      </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>comme</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr"/>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>nom, noms</t>
+          <t>comme (forme partagée)</t>
         </is>
       </c>
       <c r="F211" s="6" t="inlineStr">
@@ -6635,18 +6636,18 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>pourquoi</t>
+          <t>perdre</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr"/>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>pourquoi (forme partagée)</t>
+          <t>perdre, perdu (forme partagée), perd, perds, perdue (forme partagée), perdait, perdus (forme partagée), perdez (+27 autres formes)</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
@@ -6663,22 +6664,18 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>la porte</t>
-        </is>
-      </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>quel</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr"/>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif interrogatif</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>porte (forme partagée), portes (forme partagée)</t>
+          <t>quel, quelles, quels</t>
         </is>
       </c>
       <c r="F213" s="6" t="inlineStr">
@@ -6695,18 +6692,22 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>comme</t>
-        </is>
-      </c>
-      <c r="C214" s="5" t="inlineStr"/>
+          <t>la mort</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>comme (forme partagée)</t>
+          <t>mort (forme partagée), morts (forme partagée)</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
@@ -6723,7 +6724,7 @@
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>perdre</t>
+          <t>jouer</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr"/>
@@ -6734,7 +6735,7 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>perdre, perdu (forme partagée), perd, perds, perdue (forme partagée), perdait, perdus (forme partagée), perdez (+27 autres formes)</t>
+          <t>jouer, joue (forme partagée), joué (forme partagée), jouait, joues (forme partagée), jouent, jouez, jouant (+24 autres formes)</t>
         </is>
       </c>
       <c r="F215" s="6" t="inlineStr">
@@ -6751,18 +6752,18 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>quel</t>
+          <t>ouvrir</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr"/>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>adjectif interrogatif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>quel</t>
+          <t>ouvrir, ouvre, ouvert (forme partagée), ouvrit, ouvrez, ouverte (forme partagée), ouvrait, ouvrant (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
@@ -6779,22 +6780,18 @@
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>la mort</t>
-        </is>
-      </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>contre</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr"/>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>mort (forme partagée), morts (forme partagée), morte (forme partagée), mortes (forme partagée)</t>
+          <t>contre (forme partagée)</t>
         </is>
       </c>
       <c r="F217" s="6" t="inlineStr">
@@ -6811,18 +6808,22 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>jouer</t>
-        </is>
-      </c>
-      <c r="C218" s="5" t="inlineStr"/>
+          <t>l'accord</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>jouer, joue (forme partagée), joué (forme partagée), jouait, joues (forme partagée), jouent, jouez, jouant (+24 autres formes)</t>
+          <t>accord, accords</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
@@ -6839,18 +6840,18 @@
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>ouvrir</t>
+          <t>devant</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr"/>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>ouvrir, ouvre, ouvert (forme partagée), ouvrit, ouvrez, ouverte (forme partagée), ouvrait, ouvrant (forme partagée) (+25 autres formes)</t>
+          <t>devant (forme partagée)</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
@@ -6867,18 +6868,18 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>contre</t>
+          <t>personne</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr"/>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>pronom indéfini</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>contre (forme partagée)</t>
+          <t>personne (forme partagée)</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
@@ -6895,22 +6896,18 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>le accord</t>
-        </is>
-      </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr"/>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>pronom indéfini</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>accord, accords</t>
+          <t>un (forme partagée), une, unes, uns</t>
         </is>
       </c>
       <c r="F221" s="6" t="inlineStr">
@@ -6927,18 +6924,18 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>devant</t>
+          <t>parce que</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr"/>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>devant (forme partagée)</t>
+          <t>parce que (forme partagée), parce qu'</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
@@ -6955,18 +6952,18 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>personne</t>
+          <t>ah</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr"/>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>pronom indéfini</t>
+          <t>onomatopée</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>personne (forme partagée)</t>
+          <t>ah</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
@@ -6983,18 +6980,22 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="C224" s="5" t="inlineStr"/>
+          <t>la peur</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>pronom indéfini</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>un (forme partagée)</t>
+          <t>peur, peurs</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
@@ -7011,18 +7012,18 @@
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>parce que</t>
+          <t>jeune</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr"/>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>parce que (forme partagée)</t>
+          <t>jeune (forme partagée), jeunes (forme partagée)</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
@@ -7039,18 +7040,22 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>ah</t>
-        </is>
-      </c>
-      <c r="C226" s="5" t="inlineStr"/>
+          <t>l'amour</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>onomatopée</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>ah</t>
+          <t>amour, amours</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
@@ -7067,22 +7072,18 @@
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>la peur</t>
-        </is>
-      </c>
-      <c r="C227" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>commencer</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr"/>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>peur, peurs</t>
+          <t>commencer, commence, commencé, commençait, commença, commencent, commençaient, commençais (+25 autres formes)</t>
         </is>
       </c>
       <c r="F227" s="6" t="inlineStr">
@@ -7099,18 +7100,22 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>jeune</t>
-        </is>
-      </c>
-      <c r="C228" s="5" t="inlineStr"/>
+          <t>le côté</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>jeune (forme partagée), jeunes (forme partagée)</t>
+          <t>côté, côtés</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
@@ -7127,22 +7132,18 @@
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>le amour</t>
-        </is>
-      </c>
-      <c r="C229" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>tomber</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr"/>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>amour, amours</t>
+          <t>tomber, tombe (forme partagée), tombé (forme partagée), tombée (forme partagée), tombait, tomba, tombent, tombés (forme partagée) (+24 autres formes)</t>
         </is>
       </c>
       <c r="F229" s="6" t="inlineStr">
@@ -7159,7 +7160,7 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>commencer</t>
+          <t>entrer</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr"/>
@@ -7170,7 +7171,7 @@
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>commencer, commence, commencé, commençait, commença, commencent, commençaient, commençais (+25 autres formes)</t>
+          <t>entrer, entre (forme partagée), entrez, entré, entra, entrait, entrée (forme partagée), entrés (+25 autres formes)</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
@@ -7187,22 +7188,18 @@
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>le côté</t>
-        </is>
-      </c>
-      <c r="C231" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>aider</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr"/>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>côté, côtés</t>
+          <t>aider, aide (forme partagée), aidez, aidé, aidera, aides (forme partagée), aidée, aidait (+24 autres formes)</t>
         </is>
       </c>
       <c r="F231" s="6" t="inlineStr">
@@ -7219,18 +7216,18 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>tomber</t>
+          <t>vite</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr"/>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>tomber, tombe (forme partagée), tombé (forme partagée), tombée (forme partagée), tombait, tomba, tombent, tombés (forme partagée) (+24 autres formes)</t>
+          <t>vite (forme partagée)</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
@@ -7247,18 +7244,18 @@
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>entrer</t>
+          <t>tes</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr"/>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adjectif possessif</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>entrer, entre (forme partagée), entrez, entré, entra, entrait, entrée (forme partagée), entrés (+25 autres formes)</t>
+          <t>tes</t>
         </is>
       </c>
       <c r="F233" s="6" t="inlineStr">
@@ -7275,18 +7272,22 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>aider</t>
-        </is>
-      </c>
-      <c r="C234" s="5" t="inlineStr"/>
+          <t>dernier</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>aider, aide (forme partagée), aidez, aidé, aidera, aides (forme partagée), aidée, aidait (+24 autres formes)</t>
+          <t>dernière (forme partagée), dernier (forme partagée), derniers (forme partagée), dernières (forme partagée)</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
@@ -7303,18 +7304,22 @@
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>vite</t>
-        </is>
-      </c>
-      <c r="C235" s="6" t="inlineStr"/>
+          <t>le mot</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>vite (forme partagée)</t>
+          <t>mot, mots</t>
         </is>
       </c>
       <c r="F235" s="6" t="inlineStr">
@@ -7331,7 +7336,7 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>tes</t>
+          <t>vos</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr"/>
@@ -7342,7 +7347,7 @@
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>tes</t>
+          <t>vos</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
@@ -7359,22 +7364,18 @@
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>dernier</t>
-        </is>
-      </c>
-      <c r="C237" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>assez</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr"/>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>dernière (forme partagée), dernier (forme partagée), derniers (forme partagée), dernières (forme partagée)</t>
+          <t>assez</t>
         </is>
       </c>
       <c r="F237" s="6" t="inlineStr">
@@ -7391,22 +7392,18 @@
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>le mot</t>
-        </is>
-      </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>tant</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr"/>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>mot, mots</t>
+          <t>tant</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
@@ -7423,18 +7420,18 @@
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>vos</t>
+          <t>peu</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr"/>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>adjectif possessif</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>vos</t>
+          <t>peu (forme partagée)</t>
         </is>
       </c>
       <c r="F239" s="6" t="inlineStr">
@@ -7451,18 +7448,18 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>assez</t>
+          <t>rentrer</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr"/>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>assez</t>
+          <t>rentrer, rentre, rentré (forme partagée), rentrée (forme partagée), rentrez, rentrant (forme partagée), rentres, rentrons (+24 autres formes)</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
@@ -7479,18 +7476,18 @@
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>tant</t>
+          <t>juste</t>
         </is>
       </c>
       <c r="C241" s="6" t="inlineStr"/>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>tant</t>
+          <t>juste (forme partagée), justes (forme partagée)</t>
         </is>
       </c>
       <c r="F241" s="6" t="inlineStr">
@@ -7507,7 +7504,7 @@
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>peu</t>
+          <t>mal</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr"/>
@@ -7518,7 +7515,7 @@
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>peu (forme partagée)</t>
+          <t>mal (forme partagée)</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
@@ -7535,7 +7532,7 @@
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>rentrer</t>
+          <t>sembler</t>
         </is>
       </c>
       <c r="C243" s="6" t="inlineStr"/>
@@ -7546,7 +7543,7 @@
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>rentrer, rentre, rentré (forme partagée), rentrée (forme partagée), rentrez, rentrant (forme partagée), rentres, rentrons (+24 autres formes)</t>
+          <t>sembler, semblait, semble, semblaient, semblent, sembla, semblé, semblant (forme partagée) (+12 autres formes)</t>
         </is>
       </c>
       <c r="F243" s="6" t="inlineStr">
@@ -7563,18 +7560,18 @@
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>juste</t>
+          <t>eux</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr"/>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>juste (forme partagée), justes (forme partagée)</t>
+          <t>eux</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
@@ -7591,18 +7588,18 @@
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>mal</t>
+          <t>tirer</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr"/>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>mal (forme partagée)</t>
+          <t>tirer, tire (forme partagée), tiré (forme partagée), tirez, tira, tirait, tirant (forme partagée), tirent (+25 autres formes)</t>
         </is>
       </c>
       <c r="F245" s="6" t="inlineStr">
@@ -7619,18 +7616,22 @@
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>sembler</t>
-        </is>
-      </c>
-      <c r="C246" s="5" t="inlineStr"/>
+          <t>vieux</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>sembler, semblait, semble, semblaient, semblent, sembla, semblé, semblant (forme partagée) (+12 autres formes)</t>
+          <t>vieux (forme partagée), vieille (forme partagée), vieilles (forme partagée), vieil</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
@@ -7647,18 +7648,18 @@
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>porter</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr"/>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>comment (forme partagée)</t>
+          <t>porter (forme partagée), porte (forme partagée), portait, porté, portant (forme partagée), portaient, portent, portes (forme partagée) (+24 autres formes)</t>
         </is>
       </c>
       <c r="F247" s="6" t="inlineStr">
@@ -7675,18 +7676,18 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>eux</t>
+          <t>écouter</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr"/>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>eux</t>
+          <t>écouter, écoute (forme partagée), écoutez, écoutait, écouté, écoutes (forme partagée), écoutant (forme partagée), écoutais (+23 autres formes)</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
@@ -7703,18 +7704,22 @@
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>tirer</t>
-        </is>
-      </c>
-      <c r="C249" s="6" t="inlineStr"/>
+          <t>la raison</t>
+        </is>
+      </c>
+      <c r="C249" s="6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>tirer, tire (forme partagée), tiré (forme partagée), tirez, tira, tirait, tirant (forme partagée), tirent (+25 autres formes)</t>
+          <t>raison, raisons</t>
         </is>
       </c>
       <c r="F249" s="6" t="inlineStr">
@@ -7731,22 +7736,18 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>vieux</t>
-        </is>
-      </c>
-      <c r="C250" s="5" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>oublier</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="inlineStr"/>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>adjectif</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>vieux (forme partagée), vieille (forme partagée), vieilles (forme partagée)</t>
+          <t>oublier, oublié (forme partagée), oublie (forme partagée), oubliez, oublierai, oublies (forme partagée), oubliais, oubliée (forme partagée) (+25 autres formes)</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
@@ -7763,18 +7764,22 @@
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>porter</t>
-        </is>
-      </c>
-      <c r="C251" s="6" t="inlineStr"/>
+          <t>la place</t>
+        </is>
+      </c>
+      <c r="C251" s="6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>porter (forme partagée), porte (forme partagée), portait, porté, portant (forme partagée), portaient, portent, portes (forme partagée) (+24 autres formes)</t>
+          <t>place (forme partagée), places (forme partagée)</t>
         </is>
       </c>
       <c r="F251" s="6" t="inlineStr">
@@ -7791,18 +7796,22 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>écouter</t>
-        </is>
-      </c>
-      <c r="C252" s="5" t="inlineStr"/>
+          <t>le fait</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>écouter, écoute (forme partagée), écoutez, écoutait, écouté, écoutes (forme partagée), écoutant (forme partagée), écoutais (+23 autres formes)</t>
+          <t>fait (forme partagée), faits (forme partagée)</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
@@ -7819,7 +7828,7 @@
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>la raison</t>
+          <t>l'eau</t>
         </is>
       </c>
       <c r="C253" s="6" t="inlineStr">
@@ -7834,7 +7843,7 @@
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>raison, raisons</t>
+          <t>eau, eaux</t>
         </is>
       </c>
       <c r="F253" s="6" t="inlineStr">
@@ -7851,18 +7860,18 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>oublier</t>
+          <t>pendant</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr"/>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>préposition</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>oublier, oublié (forme partagée), oublie (forme partagée), oubliez, oublierai, oublies (forme partagée), oubliais, oubliée (forme partagée) (+25 autres formes)</t>
+          <t>pendant (forme partagée)</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
@@ -7879,22 +7888,18 @@
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>la place</t>
-        </is>
-      </c>
-      <c r="C255" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>quelqu'un</t>
+        </is>
+      </c>
+      <c r="C255" s="6" t="inlineStr"/>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>pronom indéfini</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>place (forme partagée), places (forme partagée)</t>
+          <t>quelqu'un</t>
         </is>
       </c>
       <c r="F255" s="6" t="inlineStr">
@@ -7911,22 +7916,18 @@
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>le fait</t>
-        </is>
-      </c>
-      <c r="C256" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>quelle</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="inlineStr"/>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif interrogatif</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>fait (forme partagée), faits (forme partagée)</t>
+          <t>quelle</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
@@ -7943,22 +7944,18 @@
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>la eau</t>
-        </is>
-      </c>
-      <c r="C257" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>manger</t>
+        </is>
+      </c>
+      <c r="C257" s="6" t="inlineStr"/>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>eau, eaux</t>
+          <t>manger (forme partagée), mange, mangé, mangeait, manges, mangent, mangez, mangeant (+26 autres formes)</t>
         </is>
       </c>
       <c r="F257" s="6" t="inlineStr">
@@ -7975,18 +7972,22 @@
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>pendant</t>
-        </is>
-      </c>
-      <c r="C258" s="5" t="inlineStr"/>
+          <t>la terre</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>préposition</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>pendant (forme partagée)</t>
+          <t>terre (forme partagée), terres (forme partagée)</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
@@ -8003,18 +8004,18 @@
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>quelqu'un</t>
+          <t>plaire</t>
         </is>
       </c>
       <c r="C259" s="6" t="inlineStr"/>
       <c r="D259" s="6" t="inlineStr">
         <is>
-          <t>pronom indéfini</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>quelqu'un</t>
+          <t>plaire, plaît, plaisait, plais, plairait, plaira, plaisent, plaise (+20 autres formes)</t>
         </is>
       </c>
       <c r="F259" s="6" t="inlineStr">
@@ -8031,18 +8032,22 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>quelle</t>
-        </is>
-      </c>
-      <c r="C260" s="5" t="inlineStr"/>
+          <t>la voix</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>adjectif interrogatif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>quelle</t>
+          <t>voix</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
@@ -8059,18 +8064,22 @@
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>manger</t>
-        </is>
-      </c>
-      <c r="C261" s="6" t="inlineStr"/>
+          <t>la question</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D261" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>manger (forme partagée), mange, mangé, mangeait, manges, mangent, mangez, mangeant (+26 autres formes)</t>
+          <t>question, questions</t>
         </is>
       </c>
       <c r="F261" s="6" t="inlineStr">
@@ -8087,22 +8096,18 @@
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>la terre</t>
-        </is>
-      </c>
-      <c r="C262" s="5" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>chaque</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr"/>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adjectif indéfini</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>terre (forme partagée), terres (forme partagée)</t>
+          <t>chaque</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
@@ -8119,18 +8124,22 @@
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>plaire</t>
-        </is>
-      </c>
-      <c r="C263" s="6" t="inlineStr"/>
+          <t>le corps</t>
+        </is>
+      </c>
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D263" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>plaire, plaît, plaisait, plais, plairait, plaira, plaisent, plaise (+20 autres formes)</t>
+          <t>corps</t>
         </is>
       </c>
       <c r="F263" s="6" t="inlineStr">
@@ -8147,12 +8156,12 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>la voix</t>
+          <t>le fils</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
@@ -8162,7 +8171,7 @@
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>voix</t>
+          <t>fils (forme partagée)</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
@@ -8179,7 +8188,7 @@
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>la question</t>
+          <t>la rue</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
@@ -8194,7 +8203,7 @@
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>question, questions</t>
+          <t>rue (forme partagée), rues (forme partagée)</t>
         </is>
       </c>
       <c r="F265" s="6" t="inlineStr">
@@ -8211,18 +8220,22 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>chaque</t>
-        </is>
-      </c>
-      <c r="C266" s="5" t="inlineStr"/>
+          <t>l'histoire</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>adjectif indéfini</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>chaque</t>
+          <t>histoire, histoires</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
@@ -8239,22 +8252,18 @@
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>le corps</t>
-        </is>
-      </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>répondre</t>
+        </is>
+      </c>
+      <c r="C267" s="6" t="inlineStr"/>
       <c r="D267" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>répondre, répondit, répondu, réponds, répond, répondait, répondez, répondis (+23 autres formes)</t>
         </is>
       </c>
       <c r="F267" s="6" t="inlineStr">
@@ -8271,12 +8280,12 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>le fils</t>
+          <t>l'idée</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
@@ -8286,7 +8295,7 @@
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>fils (forme partagée)</t>
+          <t>idée, idées</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
@@ -8303,22 +8312,18 @@
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>la rue</t>
-        </is>
-      </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>asseoir</t>
+        </is>
+      </c>
+      <c r="C269" s="6" t="inlineStr"/>
       <c r="D269" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>rue (forme partagée), rues (forme partagée)</t>
+          <t>asseoir, assis (forme partagée), assieds, asseyez, assise (forme partagée), assit, assied, asseyait (+35 autres formes)</t>
         </is>
       </c>
       <c r="F269" s="6" t="inlineStr">
@@ -8335,7 +8340,7 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>la histoire</t>
+          <t>la voiture</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
@@ -8350,7 +8355,7 @@
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>histoire, histoires</t>
+          <t>voiture (forme partagée), voitures (forme partagée)</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
@@ -8367,7 +8372,7 @@
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>répondre</t>
+          <t>retrouver</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr"/>
@@ -8378,7 +8383,7 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>répondre, répondit, répondu, réponds, répond, répondait, répondez, répondis (+23 autres formes)</t>
+          <t>retrouver, retrouve, retrouvé, retrouvait, retrouva, retrouvée, retrouvés, retrouvera (+25 autres formes)</t>
         </is>
       </c>
       <c r="F271" s="6" t="inlineStr">
@@ -8395,22 +8400,18 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>la idée</t>
-        </is>
-      </c>
-      <c r="C272" s="5" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>leur</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr"/>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>pronom personnel</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>idée, idées</t>
+          <t>leur (forme partagée)</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
@@ -8427,18 +8428,18 @@
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>asseoir</t>
+          <t>leur</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr"/>
       <c r="D273" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>pronom possessif</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>asseoir, assis (forme partagée), assieds, asseyez, assise (forme partagée), assit, assied, asseyait (+35 autres formes)</t>
+          <t>leur (forme partagée), leurs</t>
         </is>
       </c>
       <c r="F273" s="6" t="inlineStr">
@@ -8455,12 +8456,12 @@
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>la voiture</t>
+          <t>l'argent</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
@@ -8470,7 +8471,7 @@
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>voiture (forme partagée), voitures (forme partagée)</t>
+          <t>argent (forme partagée)</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
@@ -8487,18 +8488,18 @@
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>retrouver</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr"/>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>conjonction</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>retrouver, retrouve, retrouvé, retrouvait, retrouva, retrouvée, retrouvés, retrouvera (+25 autres formes)</t>
+          <t>car (forme partagée)</t>
         </is>
       </c>
       <c r="F275" s="6" t="inlineStr">
@@ -8515,18 +8516,22 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>leur</t>
-        </is>
-      </c>
-      <c r="C276" s="5" t="inlineStr"/>
+          <t>le visage</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>pronom personnel</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>leur (forme partagée)</t>
+          <t>visage, visages</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
@@ -8543,18 +8548,18 @@
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>leur</t>
+          <t>enfin</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr"/>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>pronom possessif</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>leur (forme partagée)</t>
+          <t>enfin</t>
         </is>
       </c>
       <c r="F277" s="6" t="inlineStr">
@@ -8571,12 +8576,12 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>le argent</t>
+          <t>la chambre</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -8586,7 +8591,7 @@
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>argent (forme partagée), argents</t>
+          <t>chambre (forme partagée), chambres (forme partagée)</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
@@ -8603,18 +8608,18 @@
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>loin</t>
         </is>
       </c>
       <c r="C279" s="6" t="inlineStr"/>
       <c r="D279" s="6" t="inlineStr">
         <is>
-          <t>conjonction</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>car (forme partagée)</t>
+          <t>loin</t>
         </is>
       </c>
       <c r="F279" s="6" t="inlineStr">
@@ -8631,7 +8636,7 @@
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>le visage</t>
+          <t>le pied</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
@@ -8646,7 +8651,7 @@
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>visage, visages</t>
+          <t>pied, pieds</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
@@ -8663,7 +8668,7 @@
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>enfin</t>
+          <t>tard</t>
         </is>
       </c>
       <c r="C281" s="6" t="inlineStr"/>
@@ -8674,7 +8679,7 @@
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>enfin</t>
+          <t>tard (forme partagée)</t>
         </is>
       </c>
       <c r="F281" s="6" t="inlineStr">
@@ -8691,7 +8696,7 @@
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>la chambre</t>
+          <t>l'année</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
@@ -8706,7 +8711,7 @@
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>chambre (forme partagée), chambres (forme partagée)</t>
+          <t>années, année</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
@@ -8723,18 +8728,18 @@
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>loin</t>
+          <t>marcher</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr"/>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>loin</t>
+          <t>marcher, marche (forme partagée), marché (forme partagée), marchait, marchant (forme partagée), marchent, marcha, marchera (+23 autres formes)</t>
         </is>
       </c>
       <c r="F283" s="6" t="inlineStr">
@@ -8751,12 +8756,12 @@
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>le pied</t>
+          <t>la maman</t>
         </is>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -8766,7 +8771,7 @@
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>pied, pieds</t>
+          <t>maman, mamans</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
@@ -8783,18 +8788,18 @@
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>tard</t>
+          <t>travailler</t>
         </is>
       </c>
       <c r="C285" s="6" t="inlineStr"/>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>tard (forme partagée)</t>
+          <t>travailler, travaille, travaillé (forme partagée), travaillait, travaillent, travaillez, travailles, travaillais (+25 autres formes)</t>
         </is>
       </c>
       <c r="F285" s="6" t="inlineStr">
@@ -8811,22 +8816,18 @@
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>la année</t>
-        </is>
-      </c>
-      <c r="C286" s="5" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>monter</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr"/>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>années, année</t>
+          <t>monter, monte, montait, monté (forme partagée), monta, montaient, montée (forme partagée), montent (+23 autres formes)</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
@@ -8843,18 +8844,18 @@
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>marcher</t>
+          <t>seulement</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr"/>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>marcher, marche (forme partagée), marché (forme partagée), marchait, marchant (forme partagée), marchent, marcha, marchera (+23 autres formes)</t>
+          <t>seulement</t>
         </is>
       </c>
       <c r="F287" s="6" t="inlineStr">
@@ -8871,22 +8872,18 @@
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>la maman</t>
-        </is>
-      </c>
-      <c r="C288" s="5" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>ainsi</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr"/>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>maman, mamans</t>
+          <t>ainsi</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
@@ -8903,18 +8900,22 @@
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>travailler</t>
-        </is>
-      </c>
-      <c r="C289" s="6" t="inlineStr"/>
+          <t>le matin</t>
+        </is>
+      </c>
+      <c r="C289" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>travailler, travaille, travaillé (forme partagée), travaillait, travaillent, travaillez, travailles, travaillais (+25 autres formes)</t>
+          <t>matin, matins</t>
         </is>
       </c>
       <c r="F289" s="6" t="inlineStr">
@@ -8931,18 +8932,22 @@
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>monter</t>
-        </is>
-      </c>
-      <c r="C290" s="5" t="inlineStr"/>
+          <t>la famille</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>monter, monte, montait, monté (forme partagée), monta, montaient, montée (forme partagée), montent (+23 autres formes)</t>
+          <t>famille, familles</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
@@ -8959,18 +8964,18 @@
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>seulement</t>
+          <t>changer</t>
         </is>
       </c>
       <c r="C291" s="6" t="inlineStr"/>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>seulement</t>
+          <t>changer, changé (forme partagée), change (forme partagée), changera, changeait, changent, changea, changez (+24 autres formes)</t>
         </is>
       </c>
       <c r="F291" s="6" t="inlineStr">
@@ -8987,18 +8992,22 @@
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>ainsi</t>
-        </is>
-      </c>
-      <c r="C292" s="5" t="inlineStr"/>
+          <t>le travail</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>ainsi</t>
+          <t>travail, travaux</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
@@ -9015,22 +9024,18 @@
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>le matin</t>
-        </is>
-      </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>dormir</t>
+        </is>
+      </c>
+      <c r="C293" s="6" t="inlineStr"/>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>matin, matins</t>
+          <t>dormir, dort, dors, dormi, dormait, dormais, dorment, dormez (+23 autres formes)</t>
         </is>
       </c>
       <c r="F293" s="6" t="inlineStr">
@@ -9047,7 +9052,7 @@
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>la famille</t>
+          <t>la ville</t>
         </is>
       </c>
       <c r="C294" s="5" t="inlineStr">
@@ -9062,7 +9067,7 @@
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>famille, familles</t>
+          <t>ville, villes</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
@@ -9079,7 +9084,7 @@
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>changer</t>
+          <t>écrire</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr"/>
@@ -9090,7 +9095,7 @@
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>changer, changé (forme partagée), change (forme partagée), changera, changeait, changent, changea, changez (+24 autres formes)</t>
+          <t>écrire, écrit (forme partagée), écris, écrivait, écrivais, écrivez, écrite (forme partagée), écrivit (+25 autres formes)</t>
         </is>
       </c>
       <c r="F295" s="6" t="inlineStr">
@@ -9107,22 +9112,18 @@
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
-          <t>le travail</t>
-        </is>
-      </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>presque</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="inlineStr"/>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>adverbe</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>travail, travaux</t>
+          <t>presque</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
@@ -9139,18 +9140,22 @@
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>dormir</t>
-        </is>
-      </c>
-      <c r="C297" s="6" t="inlineStr"/>
+          <t>l'affaire</t>
+        </is>
+      </c>
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
         <is>
-          <t>dormir, dort, dors, dormi, dormait, dormais, dorment, dormez (+23 autres formes)</t>
+          <t>affaire (forme partagée), affaires (forme partagée)</t>
         </is>
       </c>
       <c r="F297" s="6" t="inlineStr">
@@ -9167,12 +9172,12 @@
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
-          <t>la ville</t>
+          <t>le cœur</t>
         </is>
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -9182,7 +9187,7 @@
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>ville, villes</t>
+          <t>cœur, cœurs</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
@@ -9199,18 +9204,22 @@
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>écrire</t>
-        </is>
-      </c>
-      <c r="C299" s="6" t="inlineStr"/>
+          <t>le bras</t>
+        </is>
+      </c>
+      <c r="C299" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>verbe</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="E299" s="6" t="inlineStr">
         <is>
-          <t>écrire, écrit (forme partagée), écris, écrivait, écrivais, écrivez, écrite (forme partagée), écrivit (+25 autres formes)</t>
+          <t>bras</t>
         </is>
       </c>
       <c r="F299" s="6" t="inlineStr">
@@ -9227,18 +9236,18 @@
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>presque</t>
+          <t>apprendre</t>
         </is>
       </c>
       <c r="C300" s="5" t="inlineStr"/>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>adverbe</t>
+          <t>verbe</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>presque</t>
+          <t>apprendre, appris (forme partagée), apprend, apprends, apprit, apprendra, apprenait, apprennent (+25 autres formes)</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr">
@@ -9255,22 +9264,18 @@
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>la affaire</t>
-        </is>
-      </c>
-      <c r="C301" s="6" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>bon</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr"/>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>onomatopée</t>
         </is>
       </c>
       <c r="E301" s="6" t="inlineStr">
         <is>
-          <t>affaire (forme partagée), affaires (forme partagée)</t>
+          <t>bon (forme partagée)</t>
         </is>
       </c>
       <c r="F301" s="6" t="inlineStr">
@@ -9293,4 +9298,1103 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="100" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Op #</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Lemma / POS</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>je [PRO:per]</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["j'"], "lemma": "je", "pos": "PRO:per"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>ne [ADV]</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>{"keep_forms": ["ne", "n'"], "lemma": "ne", "pos": "ADV", "remove_forms": ["n"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>me [PRO:per]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["m'"], "lemma": "me", "pos": "PRO:per"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ce [PRO:dem]</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["c'"], "lemma": "ce", "pos": "PRO:dem"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>que [PRO:int]</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["qu'"], "lemma": "que", "pos": "PRO:int"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>que [PRO:rel]</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["qu'"], "lemma": "que", "pos": "PRO:rel"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>tout [ADJ], tout [ADJ:ind] → tout [ADJ:ind]</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>{"from": [{"lemma": "tout", "pos": "ADJ"}, {"lemma": "tout", "pos": "ADJ:ind"}], "into": {"forms": ["tout", "tous", "toute", "toutes"], "lemma": "tout", "pos": "ADJ:ind"}, "op": "merge"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>tout [PRO:ind]</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["tous"], "lemma": "tout", "pos": "PRO:ind"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>le [PRO:per]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["l'"], "lemma": "le", "pos": "PRO:per"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>la [PRO:per]</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["l'"], "lemma": "la", "pos": "PRO:per"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>où [PRO:int]</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>{"lemma": "où", "note": "interrogative adverb; keep the relative PRO:rel row", "pos": "PRO:int", "set_pos": "ADV"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>falloir [VER]</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["faille"], "lemma": "falloir", "pos": "VER"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>si [CON]</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["s'"], "lemma": "si", "pos": "CON"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>quoi [ADJ]</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>{"lemma": "quoi", "op": "delete", "pos": "ADJ", "reason": "quoi is not an adjective; keep PRO:int and PRO:rel"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>dont [PRO:int]</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>{"lemma": "dont", "op": "delete", "pos": "PRO:int", "reason": "dont is only relative; keep the relative row"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>comment [CON]</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>{"lemma": "comment", "op": "delete", "pos": "CON", "reason": "comment is an adverb; duplicate of the ADV row"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>est-ce que [ADV]</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["est-ce qu'"], "lemma": "est-ce que", "note": "interrogative locution", "pos": "ADV", "set_pos": "LOC:int"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>beau [ADJ]</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["bel"], "lemma": "beau", "pos": "ADJ"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>autre [PRO:ind]</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["autres"], "lemma": "autre", "pos": "PRO:ind"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>leurs [ADJ:pos]</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["leur"], "display_headword": "leur / leurs", "lemma": "leurs", "pos": "ADJ:pos"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>leur [PRO:pos]</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["leurs"], "lemma": "leur", "pos": "PRO:pos"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>quel [ADJ:int]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["quels", "quelles"], "lemma": "quel", "pos": "ADJ:int"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>un [PRO:ind]</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["une", "uns", "unes"], "lemma": "un", "pos": "PRO:ind"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>parce que [CON]</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>{"add_forms": ["parce qu'"], "lemma": "parce que", "pos": "CON"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>vieux [ADJ]</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>{"gender": "m", "lemma": "vieux", "pos": "ADJ", "set_forms": ["vieux", "vieil", "vieille", "vieilles"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>mort [NOM]</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>{"lemma": "mort", "note": "morte/mortes belong to the adjective/noun le mort, la morte", "pos": "NOM", "set_forms": ["mort", "morts"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>oeil [NOM]</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'œil", "gender": "m", "lemma": "oeil", "pos": "NOM", "set_forms": ["œil", "yeux"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>homme [NOM]</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'homme", "lemma": "homme", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>heure [NOM]</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'heure", "lemma": "heure", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>an [NOM]</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'an", "lemma": "an", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>enfant [NOM]</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'enfant", "gender": "m/f", "lemma": "enfant", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>air [NOM]</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'air", "lemma": "air", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>ami [NOM]</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'ami(e)", "gender": "m/f", "lemma": "ami", "pos": "NOM", "set_forms": ["ami", "amie", "amis", "amies"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>gens [NOM]</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "les gens", "gender": "m", "lemma": "gens", "note": "plural only; feminine for a preceding adjective: les vieilles gens", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>accord [NOM]</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'accord", "lemma": "accord", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>amour [NOM]</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'amour", "lemma": "amour", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>eau [NOM]</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'eau", "lemma": "eau", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>histoire [NOM]</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'histoire", "lemma": "histoire", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>idée [NOM]</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'idée", "lemma": "idée", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>argent [NOM]</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'argent", "lemma": "argent", "pos": "NOM", "set_forms": ["argent"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>année [NOM]</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'année", "lemma": "année", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>affaire [NOM]</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>applied</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>{"display_headword": "l'affaire", "lemma": "affaire", "pos": "NOM"}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E43"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/review-sheet.xlsx
+++ b/data/review-sheet.xlsx
@@ -10,10 +10,13 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Mots" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="À revérifier" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mots'!$A$1:$H$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Changes'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'À revérifier'!$A$1:$G$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -85,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -106,6 +109,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2840,7 +2846,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>la chose</t>
+          <t>chose</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -3300,7 +3306,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>le jour</t>
+          <t>jour</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -3448,7 +3454,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>le temps</t>
+          <t>temps</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -3788,7 +3794,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>la femme</t>
+          <t>femme</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -3820,7 +3826,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>la fois</t>
+          <t>fois</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -3908,7 +3914,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>le peu</t>
+          <t>peu</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -4000,7 +4006,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>la vie</t>
+          <t>vie</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4092,7 +4098,7 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>la main</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -4300,7 +4306,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>le père</t>
+          <t>père</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -4416,7 +4422,7 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>le monde</t>
+          <t>monde</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -4736,7 +4742,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>la mère</t>
+          <t>mère</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -4824,7 +4830,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>la fille</t>
+          <t>fille</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
@@ -4884,7 +4890,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>la tête</t>
+          <t>tête</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -5004,7 +5010,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>la nuit</t>
+          <t>nuit</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
@@ -5036,7 +5042,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>le coup</t>
+          <t>coup</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -5152,7 +5158,7 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>le dieu</t>
+          <t>dieu</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -5500,7 +5506,7 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>la maison</t>
+          <t>maison</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -5592,7 +5598,7 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>soir</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -5680,7 +5686,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>le moment</t>
+          <t>moment</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -5996,7 +6002,7 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>le monsieur</t>
+          <t>monsieur</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
@@ -6200,7 +6206,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>le besoin</t>
+          <t>besoin</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -6288,7 +6294,7 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>le les gens</t>
+          <t>les gens</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
@@ -6516,7 +6522,7 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>le nom</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
@@ -6576,7 +6582,7 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>la porte</t>
+          <t>porte</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
@@ -6692,7 +6698,7 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>la mort</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
@@ -6980,7 +6986,7 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>la peur</t>
+          <t>peur</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
@@ -7100,7 +7106,7 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>le côté</t>
+          <t>côté</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
@@ -7304,7 +7310,7 @@
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>le mot</t>
+          <t>mot</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
@@ -7704,7 +7710,7 @@
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>la raison</t>
+          <t>raison</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
@@ -7764,7 +7770,7 @@
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>la place</t>
+          <t>place</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
@@ -7796,7 +7802,7 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>le fait</t>
+          <t>fait</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
@@ -7972,7 +7978,7 @@
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>la terre</t>
+          <t>terre</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
@@ -8032,7 +8038,7 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>la voix</t>
+          <t>voix</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
@@ -8064,7 +8070,7 @@
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>la question</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr">
@@ -8124,7 +8130,7 @@
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>le corps</t>
+          <t>corps</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr">
@@ -8156,7 +8162,7 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>le fils</t>
+          <t>fils</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -8188,7 +8194,7 @@
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>la rue</t>
+          <t>rue</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
@@ -8340,7 +8346,7 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>la voiture</t>
+          <t>voiture</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
@@ -8516,7 +8522,7 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>le visage</t>
+          <t>visage</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
@@ -8576,7 +8582,7 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>la chambre</t>
+          <t>chambre</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -8636,7 +8642,7 @@
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>le pied</t>
+          <t>pied</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
@@ -8756,7 +8762,7 @@
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>la maman</t>
+          <t>maman</t>
         </is>
       </c>
       <c r="C284" s="5" t="inlineStr">
@@ -8900,7 +8906,7 @@
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>matin</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
@@ -8932,7 +8938,7 @@
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>la famille</t>
+          <t>famille</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
@@ -8992,7 +8998,7 @@
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>le travail</t>
+          <t>travail</t>
         </is>
       </c>
       <c r="C292" s="5" t="inlineStr">
@@ -9052,7 +9058,7 @@
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>la ville</t>
+          <t>ville</t>
         </is>
       </c>
       <c r="C294" s="5" t="inlineStr">
@@ -9172,7 +9178,7 @@
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
-          <t>le cœur</t>
+          <t>cœur</t>
         </is>
       </c>
       <c r="C298" s="5" t="inlineStr">
@@ -9204,7 +9210,7 @@
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>le bras</t>
+          <t>bras</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
@@ -9264,18 +9270,22 @@
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>bon</t>
-        </is>
-      </c>
-      <c r="C301" s="6" t="inlineStr"/>
+          <t>noir</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>onomatopée</t>
+          <t>adjectif</t>
         </is>
       </c>
       <c r="E301" s="6" t="inlineStr">
         <is>
-          <t>bon (forme partagée)</t>
+          <t>noir (forme partagée), noire (forme partagée), noirs (forme partagée), noires (forme partagée)</t>
         </is>
       </c>
       <c r="F301" s="6" t="inlineStr">
@@ -10397,4 +10407,1286 @@
   <autoFilter ref="A1:E43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Sujet</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Demandes de vérification POS hors des 300 mots classés</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Ces demandes sont conservées ici pour ne pas ajouter de lignes au CSV des 300 mots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>le peu</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Confirmé par l'enseignante</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>bonjour</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Note POS : code à confirmer ; entrée hors des 300 mots classés.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Mot</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Genre</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Formes</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>je</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>pronom personnel</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>je, j'</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>adverbe</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>ne, n'</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>pronom personnel</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>me, m'</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>pronom démonstratif</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>ce, c'</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>que</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>pronom interrogatif</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>que, qu'</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>que</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>pronom relatif</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>que, qu'</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>tout</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>adjectif indéfini</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>tout, tous, toute, toutes</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>tout</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>pronom indéfini</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>tout, tous</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>le</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>pronom personnel</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>le, l'</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>la</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>pronom personnel</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>la, l'</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>où</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>adverbe</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>où</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>falloir</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>verbe</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>faut, fallait, faudrait, faudra, fallu, falloir, fallut, faille</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>conjonction</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>si, s'</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>quoi</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>adjectif</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>dont</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>pronom interrogatif</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>conjonction</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>est-ce que</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>locution interrogative</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>est-ce que, est-ce qu'</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>beau</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>adjectif</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>beau, belle, beaux, belles, bel</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>pronom indéfini</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>autre, autres</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>leur / leurs</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>adjectif possessif</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>leurs, leur</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>leur</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>pronom possessif</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>leur, leurs</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>quel</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>adjectif interrogatif</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>quel, quelles, quels</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>pronom indéfini</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>un, une, unes, uns</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>parce que</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>conjonction</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>parce que, parce qu'</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>vieux</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>adjectif</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>vieux, vieille, vieilles, vieil</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>mort, morts</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>l'œil</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>yeux, œil</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>l'homme</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>homme, hommes</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>l'heure</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>heure, heures</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>l'an</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>ans, an</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>l'enfant</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>m/f</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>enfants, enfant</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>l'air</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>air, airs</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>l'ami(e)</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>m/f</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>ami, amis, amie, amies</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>les gens</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>gens</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>l'accord</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>accord, accords</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>l'amour</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>amour, amours</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>l'eau</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>eau, eaux</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>l'histoire</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>histoire, histoires</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>l'idée</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>idée, idées</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>l'argent</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>argent</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>l'année</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>années, année</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>l'affaire</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>affaire, affaires</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>cœur</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>cœur, cœurs</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Réapprovisionnement — rang Lexique 301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>bras</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>bras</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Réapprovisionnement — rang Lexique 302</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>apprendre</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>verbe</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>appris, apprendre, apprend, apprends, apprit, apprendra, apprenait, apprennent, apprendrai, apprenne, apprenant, apprenez</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Réapprovisionnement — rang Lexique 303</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>noir</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>adjectif</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>noir, noire, noirs, noires</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Réapprovisionnement — rang Lexique 305</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G47"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choisissez OK, Faux ou À corriger." type="list">
+      <formula1>"OK,Faux,À corriger"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>